--- a/excel-files/PASAY/PASAY CITY NATIONAL HIGH SCHOOL.xlsx
+++ b/excel-files/PASAY/PASAY CITY NATIONAL HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="238" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D50542B0-90E3-404F-AB1B-03D54CFC98C2}"/>
+  <xr:revisionPtr revIDLastSave="291" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A85C88F-42FB-409A-B531-4EB525BE09EA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="91">
   <si>
     <t>Grade Level</t>
   </si>
@@ -317,7 +317,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -424,8 +424,15 @@
       <name val="Bookman Old Style"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FF000000"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -496,6 +503,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF2D0"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -628,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -744,6 +757,16 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4422,11 +4445,9 @@
         <v>14</v>
       </c>
       <c r="C51" s="10">
-        <v>545</v>
-      </c>
-      <c r="D51" s="10">
-        <v>630</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="D51" s="10"/>
       <c r="E51" s="10">
         <v>2025</v>
       </c>
@@ -4435,11 +4456,11 @@
       </c>
       <c r="G51" s="3">
         <f t="shared" ref="G51:G59" si="10">IF((C51-D51)&lt;0,0,C51-D51)</f>
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="H51" s="4">
         <f t="shared" ref="H51:H59" si="11">IF((D51-C51)&lt;0,0,D51-C51)</f>
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="27.75" customHeight="1">
@@ -4450,14 +4471,18 @@
         <v>15</v>
       </c>
       <c r="C52" s="10">
-        <v>545</v>
+        <v>621</v>
       </c>
       <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="12"/>
+      <c r="E52" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G52" s="3">
         <f t="shared" si="10"/>
-        <v>545</v>
+        <v>621</v>
       </c>
       <c r="H52" s="4">
         <f t="shared" si="11"/>
@@ -4472,14 +4497,18 @@
         <v>12</v>
       </c>
       <c r="C53" s="10">
-        <v>545</v>
+        <v>621</v>
       </c>
       <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="12"/>
+      <c r="E53" s="10">
+        <v>2024</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G53" s="3">
         <f t="shared" si="10"/>
-        <v>545</v>
+        <v>621</v>
       </c>
       <c r="H53" s="4">
         <f t="shared" si="11"/>
@@ -4494,14 +4523,18 @@
         <v>21</v>
       </c>
       <c r="C54" s="10">
-        <v>545</v>
+        <v>621</v>
       </c>
       <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="12"/>
+      <c r="E54" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G54" s="3">
         <f t="shared" si="10"/>
-        <v>545</v>
+        <v>621</v>
       </c>
       <c r="H54" s="4">
         <f t="shared" si="11"/>
@@ -4516,11 +4549,9 @@
         <v>16</v>
       </c>
       <c r="C55" s="10">
-        <v>545</v>
-      </c>
-      <c r="D55" s="10">
-        <v>630</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="D55" s="10"/>
       <c r="E55" s="10">
         <v>2025</v>
       </c>
@@ -4529,11 +4560,11 @@
       </c>
       <c r="G55" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="H55" s="4">
         <f t="shared" si="11"/>
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="27.75" customHeight="1">
@@ -4544,14 +4575,18 @@
         <v>13</v>
       </c>
       <c r="C56" s="10">
-        <v>545</v>
+        <v>621</v>
       </c>
       <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="12"/>
+      <c r="E56" s="10">
+        <v>2024</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G56" s="3">
         <f t="shared" si="10"/>
-        <v>545</v>
+        <v>621</v>
       </c>
       <c r="H56" s="4">
         <f t="shared" si="11"/>
@@ -4566,11 +4601,9 @@
         <v>17</v>
       </c>
       <c r="C57" s="10">
-        <v>545</v>
-      </c>
-      <c r="D57" s="10">
-        <v>630</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="D57" s="10"/>
       <c r="E57" s="10">
         <v>2025</v>
       </c>
@@ -4579,11 +4612,11 @@
       </c>
       <c r="G57" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="H57" s="4">
         <f t="shared" si="11"/>
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="27.75" customHeight="1">
@@ -4594,14 +4627,18 @@
         <v>22</v>
       </c>
       <c r="C58" s="10">
-        <v>545</v>
+        <v>621</v>
       </c>
       <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="12"/>
+      <c r="E58" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G58" s="3">
         <f t="shared" si="10"/>
-        <v>545</v>
+        <v>621</v>
       </c>
       <c r="H58" s="4">
         <f t="shared" si="11"/>
@@ -4616,11 +4653,9 @@
         <v>19</v>
       </c>
       <c r="C59" s="10">
-        <v>545</v>
-      </c>
-      <c r="D59" s="10">
-        <v>630</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="D59" s="10"/>
       <c r="E59" s="10">
         <v>2025</v>
       </c>
@@ -4629,11 +4664,11 @@
       </c>
       <c r="G59" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="H59" s="4">
         <f t="shared" si="11"/>
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="27.75" customHeight="1">
@@ -4698,12 +4733,9 @@
         <v>12</v>
       </c>
       <c r="C63" s="10">
-        <v>478</v>
-      </c>
-      <c r="D63" s="10">
-        <f>516+3</f>
-        <v>519</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="D63" s="10"/>
       <c r="E63" s="10">
         <v>2025</v>
       </c>
@@ -4712,11 +4744,11 @@
       </c>
       <c r="G63" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="H63" s="4">
         <f t="shared" si="13"/>
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="27.75" customHeight="1">
@@ -4727,11 +4759,9 @@
         <v>21</v>
       </c>
       <c r="C64" s="10">
-        <v>478</v>
-      </c>
-      <c r="D64" s="10">
-        <v>519</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="D64" s="10"/>
       <c r="E64" s="10">
         <v>2025</v>
       </c>
@@ -4740,11 +4770,11 @@
       </c>
       <c r="G64" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="H64" s="4">
         <f t="shared" si="13"/>
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="27.75" customHeight="1">
@@ -4777,14 +4807,18 @@
         <v>13</v>
       </c>
       <c r="C66" s="10">
-        <v>478</v>
+        <v>516</v>
       </c>
       <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="12"/>
+      <c r="E66" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G66" s="3">
         <f t="shared" si="12"/>
-        <v>478</v>
+        <v>516</v>
       </c>
       <c r="H66" s="4">
         <f t="shared" si="13"/>
@@ -4897,14 +4931,18 @@
         <v>15</v>
       </c>
       <c r="C72" s="10">
-        <v>450</v>
+        <v>528</v>
       </c>
       <c r="D72" s="10"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="12"/>
+      <c r="E72" s="10">
+        <v>2024</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G72" s="3">
         <f t="shared" si="14"/>
-        <v>450</v>
+        <v>528</v>
       </c>
       <c r="H72" s="4">
         <f t="shared" si="15"/>
@@ -5105,14 +5143,18 @@
         <v>15</v>
       </c>
       <c r="C82" s="10">
-        <v>456</v>
+        <v>549</v>
       </c>
       <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="12"/>
+      <c r="E82" s="10">
+        <v>2024</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G82" s="3">
         <f t="shared" si="16"/>
-        <v>456</v>
+        <v>549</v>
       </c>
       <c r="H82" s="4">
         <f t="shared" si="17"/>
@@ -5542,38 +5584,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5737,7 +5779,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="39" customHeight="1">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -8697,7 +8739,7 @@
       <c r="B51" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C51" s="1"/>
+      <c r="C51" s="29"/>
       <c r="D51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
@@ -8760,6 +8802,7 @@
       </c>
     </row>
     <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="C52" s="42"/>
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8777,7 +8820,7 @@
       <c r="A53" s="1">
         <v>6</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="44" t="s">
         <v>14</v>
       </c>
       <c r="C53" s="1"/>
@@ -8846,7 +8889,7 @@
       <c r="A54" s="1">
         <v>6</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="44" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="1"/>
@@ -8915,7 +8958,7 @@
       <c r="A55" s="1">
         <v>6</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="44" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="1"/>
@@ -8984,7 +9027,7 @@
       <c r="A56" s="1">
         <v>6</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="44" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="1"/>
@@ -9053,7 +9096,7 @@
       <c r="A57" s="1">
         <v>6</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="44" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="1"/>
@@ -9122,7 +9165,7 @@
       <c r="A58" s="1">
         <v>6</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="44" t="s">
         <v>13</v>
       </c>
       <c r="C58" s="1"/>
@@ -9191,7 +9234,7 @@
       <c r="A59" s="1">
         <v>6</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="44" t="s">
         <v>17</v>
       </c>
       <c r="C59" s="1"/>
@@ -9260,7 +9303,7 @@
       <c r="A60" s="1">
         <v>6</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="44" t="s">
         <v>18</v>
       </c>
       <c r="C60" s="1"/>
@@ -9329,7 +9372,7 @@
       <c r="A61" s="1">
         <v>6</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="44" t="s">
         <v>19</v>
       </c>
       <c r="C61" s="1"/>
@@ -9395,6 +9438,7 @@
       </c>
     </row>
     <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+      <c r="C62" s="42"/>
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9412,22 +9456,22 @@
       <c r="A63" s="10">
         <v>7</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C63" s="10">
-        <v>545</v>
+      <c r="C63" s="43">
+        <v>621</v>
       </c>
       <c r="D63" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="10"/>
       <c r="G63" s="12"/>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="I63" s="12">
         <f t="shared" si="3"/>
@@ -9435,14 +9479,14 @@
       </c>
       <c r="J63" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="K63" s="12"/>
       <c r="L63" s="10"/>
       <c r="M63" s="12"/>
       <c r="N63" s="12">
         <f t="shared" si="10"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="O63" s="12">
         <f t="shared" si="11"/>
@@ -9450,14 +9494,14 @@
       </c>
       <c r="P63" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="Q63" s="12"/>
       <c r="R63" s="10"/>
       <c r="S63" s="12"/>
       <c r="T63" s="12">
         <f t="shared" si="12"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="U63" s="12">
         <f t="shared" si="13"/>
@@ -9465,14 +9509,14 @@
       </c>
       <c r="V63" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="W63" s="12"/>
       <c r="X63" s="10"/>
       <c r="Y63" s="12"/>
       <c r="Z63" s="12">
         <f t="shared" si="14"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="AA63" s="12">
         <f t="shared" si="15"/>
@@ -9483,22 +9527,22 @@
       <c r="A64" s="10">
         <v>7</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="10">
-        <v>545</v>
+      <c r="C64" s="43">
+        <v>621</v>
       </c>
       <c r="D64" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="10"/>
       <c r="G64" s="12"/>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="I64" s="12">
         <f t="shared" si="3"/>
@@ -9506,14 +9550,14 @@
       </c>
       <c r="J64" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="K64" s="12"/>
       <c r="L64" s="10"/>
       <c r="M64" s="12"/>
       <c r="N64" s="12">
         <f t="shared" si="10"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="O64" s="12">
         <f t="shared" si="11"/>
@@ -9521,14 +9565,14 @@
       </c>
       <c r="P64" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="Q64" s="12"/>
       <c r="R64" s="10"/>
       <c r="S64" s="12"/>
       <c r="T64" s="12">
         <f t="shared" si="12"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="U64" s="12">
         <f t="shared" si="13"/>
@@ -9536,14 +9580,14 @@
       </c>
       <c r="V64" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="W64" s="12"/>
       <c r="X64" s="10"/>
       <c r="Y64" s="12"/>
       <c r="Z64" s="12">
         <f t="shared" si="14"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="AA64" s="12">
         <f t="shared" si="15"/>
@@ -9554,22 +9598,22 @@
       <c r="A65" s="10">
         <v>7</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C65" s="10">
-        <v>545</v>
+      <c r="C65" s="43">
+        <v>621</v>
       </c>
       <c r="D65" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="10"/>
       <c r="G65" s="12"/>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="I65" s="12">
         <f t="shared" si="3"/>
@@ -9577,14 +9621,14 @@
       </c>
       <c r="J65" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="K65" s="12"/>
       <c r="L65" s="10"/>
       <c r="M65" s="12"/>
       <c r="N65" s="12">
         <f t="shared" si="10"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="O65" s="12">
         <f t="shared" si="11"/>
@@ -9592,14 +9636,14 @@
       </c>
       <c r="P65" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="Q65" s="12"/>
       <c r="R65" s="10"/>
       <c r="S65" s="12"/>
       <c r="T65" s="12">
         <f t="shared" si="12"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="U65" s="12">
         <f t="shared" si="13"/>
@@ -9607,14 +9651,14 @@
       </c>
       <c r="V65" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="W65" s="12"/>
       <c r="X65" s="10"/>
       <c r="Y65" s="12"/>
       <c r="Z65" s="12">
         <f t="shared" si="14"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="AA65" s="12">
         <f t="shared" si="15"/>
@@ -9625,22 +9669,22 @@
       <c r="A66" s="10">
         <v>7</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="10">
-        <v>545</v>
+      <c r="C66" s="43">
+        <v>621</v>
       </c>
       <c r="D66" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="10"/>
       <c r="G66" s="12"/>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="I66" s="12">
         <f t="shared" si="3"/>
@@ -9648,14 +9692,14 @@
       </c>
       <c r="J66" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="K66" s="12"/>
       <c r="L66" s="10"/>
       <c r="M66" s="12"/>
       <c r="N66" s="12">
         <f t="shared" si="10"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="O66" s="12">
         <f t="shared" si="11"/>
@@ -9663,14 +9707,14 @@
       </c>
       <c r="P66" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="Q66" s="12"/>
       <c r="R66" s="10"/>
       <c r="S66" s="12"/>
       <c r="T66" s="12">
         <f t="shared" si="12"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="U66" s="12">
         <f t="shared" si="13"/>
@@ -9678,14 +9722,14 @@
       </c>
       <c r="V66" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="W66" s="12"/>
       <c r="X66" s="10"/>
       <c r="Y66" s="12"/>
       <c r="Z66" s="12">
         <f t="shared" si="14"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="AA66" s="12">
         <f t="shared" si="15"/>
@@ -9696,22 +9740,22 @@
       <c r="A67" s="10">
         <v>7</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C67" s="10">
-        <v>545</v>
+      <c r="C67" s="43">
+        <v>621</v>
       </c>
       <c r="D67" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="10"/>
       <c r="G67" s="12"/>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="I67" s="12">
         <f t="shared" si="3"/>
@@ -9719,14 +9763,14 @@
       </c>
       <c r="J67" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="K67" s="12"/>
       <c r="L67" s="10"/>
       <c r="M67" s="12"/>
       <c r="N67" s="12">
         <f t="shared" si="10"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="O67" s="12">
         <f t="shared" si="11"/>
@@ -9734,14 +9778,14 @@
       </c>
       <c r="P67" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="Q67" s="12"/>
       <c r="R67" s="10"/>
       <c r="S67" s="12"/>
       <c r="T67" s="12">
         <f t="shared" si="12"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="U67" s="12">
         <f t="shared" si="13"/>
@@ -9749,14 +9793,14 @@
       </c>
       <c r="V67" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="W67" s="12"/>
       <c r="X67" s="10"/>
       <c r="Y67" s="12"/>
       <c r="Z67" s="12">
         <f t="shared" si="14"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="AA67" s="12">
         <f t="shared" si="15"/>
@@ -9767,22 +9811,22 @@
       <c r="A68" s="10">
         <v>7</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C68" s="10">
-        <v>545</v>
+      <c r="C68" s="43">
+        <v>621</v>
       </c>
       <c r="D68" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="10"/>
       <c r="G68" s="12"/>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="I68" s="12">
         <f t="shared" si="3"/>
@@ -9790,14 +9834,14 @@
       </c>
       <c r="J68" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="K68" s="12"/>
       <c r="L68" s="10"/>
       <c r="M68" s="12"/>
       <c r="N68" s="12">
         <f t="shared" si="10"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="O68" s="12">
         <f t="shared" si="11"/>
@@ -9805,14 +9849,14 @@
       </c>
       <c r="P68" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="Q68" s="12"/>
       <c r="R68" s="10"/>
       <c r="S68" s="12"/>
       <c r="T68" s="12">
         <f t="shared" si="12"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="U68" s="12">
         <f t="shared" si="13"/>
@@ -9820,14 +9864,14 @@
       </c>
       <c r="V68" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="W68" s="12"/>
       <c r="X68" s="10"/>
       <c r="Y68" s="12"/>
       <c r="Z68" s="12">
         <f t="shared" si="14"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="AA68" s="12">
         <f t="shared" si="15"/>
@@ -9838,22 +9882,22 @@
       <c r="A69" s="10">
         <v>7</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="C69" s="10">
-        <v>545</v>
+      <c r="C69" s="43">
+        <v>621</v>
       </c>
       <c r="D69" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="10"/>
       <c r="G69" s="12"/>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="I69" s="12">
         <f t="shared" si="3"/>
@@ -9861,14 +9905,14 @@
       </c>
       <c r="J69" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="K69" s="12"/>
       <c r="L69" s="10"/>
       <c r="M69" s="12"/>
       <c r="N69" s="12">
         <f t="shared" si="10"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="O69" s="12">
         <f t="shared" si="11"/>
@@ -9876,14 +9920,14 @@
       </c>
       <c r="P69" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="Q69" s="12"/>
       <c r="R69" s="10"/>
       <c r="S69" s="12"/>
       <c r="T69" s="12">
         <f t="shared" si="12"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="U69" s="12">
         <f t="shared" si="13"/>
@@ -9891,14 +9935,14 @@
       </c>
       <c r="V69" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="W69" s="12"/>
       <c r="X69" s="10"/>
       <c r="Y69" s="12"/>
       <c r="Z69" s="12">
         <f t="shared" si="14"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="AA69" s="12">
         <f t="shared" si="15"/>
@@ -9909,22 +9953,22 @@
       <c r="A70" s="10">
         <v>7</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C70" s="10">
-        <v>545</v>
+      <c r="C70" s="43">
+        <v>621</v>
       </c>
       <c r="D70" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="E70" s="12"/>
       <c r="F70" s="10"/>
       <c r="G70" s="12"/>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="I70" s="12">
         <f t="shared" si="3"/>
@@ -9932,14 +9976,14 @@
       </c>
       <c r="J70" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="K70" s="12"/>
       <c r="L70" s="10"/>
       <c r="M70" s="12"/>
       <c r="N70" s="12">
         <f t="shared" ref="N70:N126" si="16">IF((J70-K70)&lt;0,0,(J70-K70))</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="O70" s="12">
         <f t="shared" ref="O70:O126" si="17">IF((K70-J70)&lt;0,0,(K70-J70))</f>
@@ -9947,14 +9991,14 @@
       </c>
       <c r="P70" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="Q70" s="12"/>
       <c r="R70" s="10"/>
       <c r="S70" s="12"/>
       <c r="T70" s="12">
         <f t="shared" ref="T70:T127" si="18">IF((P70-Q70)&lt;0,0,(P70-Q70))</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="U70" s="12">
         <f t="shared" ref="U70:U127" si="19">IF((Q70-P70)&lt;0,0,(Q70-P70))</f>
@@ -9962,14 +10006,14 @@
       </c>
       <c r="V70" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="W70" s="12"/>
       <c r="X70" s="10"/>
       <c r="Y70" s="12"/>
       <c r="Z70" s="12">
         <f t="shared" ref="Z70:Z127" si="20">IF((V70-W70)&lt;0,0,(V70-W70))</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="AA70" s="12">
         <f t="shared" ref="AA70:AA127" si="21">IF((W70-V70)&lt;0,0,(W70-V70))</f>
@@ -9980,22 +10024,22 @@
       <c r="A71" s="10">
         <v>7</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C71" s="10">
-        <v>545</v>
+      <c r="C71" s="43">
+        <v>621</v>
       </c>
       <c r="D71" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="10"/>
       <c r="G71" s="12"/>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="I71" s="12">
         <f t="shared" si="3"/>
@@ -10003,14 +10047,14 @@
       </c>
       <c r="J71" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="K71" s="12"/>
       <c r="L71" s="10"/>
       <c r="M71" s="12"/>
       <c r="N71" s="12">
         <f t="shared" si="16"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="O71" s="12">
         <f t="shared" si="17"/>
@@ -10018,14 +10062,14 @@
       </c>
       <c r="P71" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="Q71" s="12"/>
       <c r="R71" s="10"/>
       <c r="S71" s="12"/>
       <c r="T71" s="12">
         <f t="shared" si="18"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="U71" s="12">
         <f t="shared" si="19"/>
@@ -10033,14 +10077,14 @@
       </c>
       <c r="V71" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="W71" s="12"/>
       <c r="X71" s="10"/>
       <c r="Y71" s="12"/>
       <c r="Z71" s="12">
         <f t="shared" si="20"/>
-        <v>4360</v>
+        <v>4968</v>
       </c>
       <c r="AA71" s="12">
         <f t="shared" si="21"/>
@@ -10048,6 +10092,7 @@
       </c>
     </row>
     <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="C72" s="42"/>
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10065,10 +10110,10 @@
       <c r="A73" s="10">
         <v>8</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C73" s="10">
+      <c r="C73" s="43">
         <v>478</v>
       </c>
       <c r="D73" s="12">
@@ -10136,10 +10181,10 @@
       <c r="A74" s="10">
         <v>8</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="C74" s="10">
+      <c r="C74" s="43">
         <v>478</v>
       </c>
       <c r="D74" s="12">
@@ -10207,22 +10252,22 @@
       <c r="A75" s="10">
         <v>8</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C75" s="10">
-        <v>478</v>
+      <c r="C75" s="43">
+        <v>516</v>
       </c>
       <c r="D75" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="E75" s="12"/>
       <c r="F75" s="10"/>
       <c r="G75" s="12"/>
       <c r="H75" s="12">
         <f t="shared" si="2"/>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="I75" s="12">
         <f t="shared" si="3"/>
@@ -10230,14 +10275,14 @@
       </c>
       <c r="J75" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="K75" s="12"/>
       <c r="L75" s="10"/>
       <c r="M75" s="12"/>
       <c r="N75" s="12">
         <f t="shared" si="16"/>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="O75" s="12">
         <f t="shared" si="17"/>
@@ -10245,14 +10290,14 @@
       </c>
       <c r="P75" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="Q75" s="12"/>
       <c r="R75" s="10"/>
       <c r="S75" s="12"/>
       <c r="T75" s="12">
         <f t="shared" si="18"/>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="U75" s="12">
         <f t="shared" si="19"/>
@@ -10260,14 +10305,14 @@
       </c>
       <c r="V75" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="W75" s="12"/>
       <c r="X75" s="10"/>
       <c r="Y75" s="12"/>
       <c r="Z75" s="12">
         <f t="shared" si="20"/>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="AA75" s="12">
         <f t="shared" si="21"/>
@@ -10278,22 +10323,22 @@
       <c r="A76" s="10">
         <v>8</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C76" s="10">
-        <v>478</v>
+      <c r="C76" s="43">
+        <v>516</v>
       </c>
       <c r="D76" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="10"/>
       <c r="G76" s="12"/>
       <c r="H76" s="12">
         <f t="shared" si="2"/>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="I76" s="12">
         <f t="shared" si="3"/>
@@ -10301,14 +10346,14 @@
       </c>
       <c r="J76" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="K76" s="12"/>
       <c r="L76" s="10"/>
       <c r="M76" s="12"/>
       <c r="N76" s="12">
         <f t="shared" si="16"/>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="O76" s="12">
         <f t="shared" si="17"/>
@@ -10316,14 +10361,14 @@
       </c>
       <c r="P76" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="Q76" s="12"/>
       <c r="R76" s="10"/>
       <c r="S76" s="12"/>
       <c r="T76" s="12">
         <f t="shared" si="18"/>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="U76" s="12">
         <f t="shared" si="19"/>
@@ -10331,14 +10376,14 @@
       </c>
       <c r="V76" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="W76" s="12"/>
       <c r="X76" s="10"/>
       <c r="Y76" s="12"/>
       <c r="Z76" s="12">
         <f t="shared" si="20"/>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="AA76" s="12">
         <f t="shared" si="21"/>
@@ -10349,10 +10394,10 @@
       <c r="A77" s="10">
         <v>8</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C77" s="10">
+      <c r="C77" s="43">
         <v>478</v>
       </c>
       <c r="D77" s="12">
@@ -10420,22 +10465,22 @@
       <c r="A78" s="10">
         <v>8</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C78" s="10">
-        <v>478</v>
+      <c r="C78" s="43">
+        <v>516</v>
       </c>
       <c r="D78" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="10"/>
       <c r="G78" s="12"/>
       <c r="H78" s="12">
         <f t="shared" ref="H78:H127" si="22">IF((D78-E78)&lt;0,0,(D78-E78))</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="I78" s="12">
         <f t="shared" ref="I78:I127" si="23">IF((E78-D78)&lt;0,0,(E78-D78))</f>
@@ -10443,14 +10488,14 @@
       </c>
       <c r="J78" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="K78" s="12"/>
       <c r="L78" s="10"/>
       <c r="M78" s="12"/>
       <c r="N78" s="12">
         <f t="shared" si="16"/>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="O78" s="12">
         <f t="shared" si="17"/>
@@ -10458,14 +10503,14 @@
       </c>
       <c r="P78" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="Q78" s="12"/>
       <c r="R78" s="10"/>
       <c r="S78" s="12"/>
       <c r="T78" s="12">
         <f t="shared" si="18"/>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="U78" s="12">
         <f t="shared" si="19"/>
@@ -10473,14 +10518,14 @@
       </c>
       <c r="V78" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="W78" s="12"/>
       <c r="X78" s="10"/>
       <c r="Y78" s="12"/>
       <c r="Z78" s="12">
         <f t="shared" si="20"/>
-        <v>3824</v>
+        <v>4128</v>
       </c>
       <c r="AA78" s="12">
         <f t="shared" si="21"/>
@@ -10491,10 +10536,10 @@
       <c r="A79" s="10">
         <v>8</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="C79" s="10">
+      <c r="C79" s="43">
         <v>478</v>
       </c>
       <c r="D79" s="12">
@@ -10562,10 +10607,10 @@
       <c r="A80" s="10">
         <v>8</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C80" s="10">
+      <c r="C80" s="43">
         <v>478</v>
       </c>
       <c r="D80" s="12">
@@ -10633,10 +10678,10 @@
       <c r="A81" s="10">
         <v>8</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C81" s="10">
+      <c r="C81" s="43">
         <v>478</v>
       </c>
       <c r="D81" s="12">
@@ -10701,6 +10746,7 @@
       </c>
     </row>
     <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="C82" s="42"/>
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10718,10 +10764,10 @@
       <c r="A83" s="10">
         <v>9</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C83" s="10">
+      <c r="C83" s="43">
         <v>450</v>
       </c>
       <c r="D83" s="12">
@@ -10789,22 +10835,22 @@
       <c r="A84" s="10">
         <v>9</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="C84" s="10">
-        <v>450</v>
+      <c r="C84" s="43">
+        <v>528</v>
       </c>
       <c r="D84" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3600</v>
+        <v>4224</v>
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="10"/>
       <c r="G84" s="12"/>
       <c r="H84" s="12">
         <f t="shared" si="22"/>
-        <v>3600</v>
+        <v>4224</v>
       </c>
       <c r="I84" s="12">
         <f t="shared" si="23"/>
@@ -10812,14 +10858,14 @@
       </c>
       <c r="J84" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3600</v>
+        <v>4224</v>
       </c>
       <c r="K84" s="12"/>
       <c r="L84" s="10"/>
       <c r="M84" s="12"/>
       <c r="N84" s="12">
         <f t="shared" si="16"/>
-        <v>3600</v>
+        <v>4224</v>
       </c>
       <c r="O84" s="12">
         <f t="shared" si="17"/>
@@ -10827,14 +10873,14 @@
       </c>
       <c r="P84" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3600</v>
+        <v>4224</v>
       </c>
       <c r="Q84" s="12"/>
       <c r="R84" s="10"/>
       <c r="S84" s="12"/>
       <c r="T84" s="12">
         <f t="shared" si="18"/>
-        <v>3600</v>
+        <v>4224</v>
       </c>
       <c r="U84" s="12">
         <f t="shared" si="19"/>
@@ -10842,14 +10888,14 @@
       </c>
       <c r="V84" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3600</v>
+        <v>4224</v>
       </c>
       <c r="W84" s="12"/>
       <c r="X84" s="10"/>
       <c r="Y84" s="12"/>
       <c r="Z84" s="12">
         <f t="shared" si="20"/>
-        <v>3600</v>
+        <v>4224</v>
       </c>
       <c r="AA84" s="12">
         <f t="shared" si="21"/>
@@ -10860,10 +10906,10 @@
       <c r="A85" s="10">
         <v>9</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C85" s="10">
+      <c r="C85" s="43">
         <v>450</v>
       </c>
       <c r="D85" s="12">
@@ -10931,10 +10977,10 @@
       <c r="A86" s="10">
         <v>9</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C86" s="10">
+      <c r="C86" s="43">
         <v>450</v>
       </c>
       <c r="D86" s="12">
@@ -11002,10 +11048,10 @@
       <c r="A87" s="10">
         <v>9</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C87" s="10">
+      <c r="C87" s="43">
         <v>450</v>
       </c>
       <c r="D87" s="12">
@@ -11073,10 +11119,10 @@
       <c r="A88" s="10">
         <v>9</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C88" s="10">
+      <c r="C88" s="43">
         <v>450</v>
       </c>
       <c r="D88" s="12">
@@ -11144,10 +11190,10 @@
       <c r="A89" s="10">
         <v>9</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="C89" s="10">
+      <c r="C89" s="43">
         <v>450</v>
       </c>
       <c r="D89" s="12">
@@ -11215,10 +11261,10 @@
       <c r="A90" s="10">
         <v>9</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C90" s="10">
+      <c r="C90" s="43">
         <v>450</v>
       </c>
       <c r="D90" s="12">
@@ -11286,10 +11332,10 @@
       <c r="A91" s="10">
         <v>9</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C91" s="10">
+      <c r="C91" s="43">
         <v>450</v>
       </c>
       <c r="D91" s="12">
@@ -11354,6 +11400,7 @@
       </c>
     </row>
     <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
+      <c r="C92" s="42"/>
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11371,10 +11418,10 @@
       <c r="A93" s="10">
         <v>10</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C93" s="10">
+      <c r="C93" s="43">
         <v>456</v>
       </c>
       <c r="D93" s="12">
@@ -11442,22 +11489,22 @@
       <c r="A94" s="10">
         <v>10</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="C94" s="10">
-        <v>456</v>
+      <c r="C94" s="43">
+        <v>549</v>
       </c>
       <c r="D94" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3648</v>
+        <v>4392</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="10"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12">
         <f>IF((D94-E94)&lt;0,0,(D94-E94))</f>
-        <v>3648</v>
+        <v>4392</v>
       </c>
       <c r="I94" s="12">
         <f>IF((E94-D94)&lt;0,0,(E94-D94))</f>
@@ -11465,14 +11512,14 @@
       </c>
       <c r="J94" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3648</v>
+        <v>4392</v>
       </c>
       <c r="K94" s="12"/>
       <c r="L94" s="10"/>
       <c r="M94" s="12"/>
       <c r="N94" s="12">
         <f>IF((J94-K94)&lt;0,0,(J94-K94))</f>
-        <v>3648</v>
+        <v>4392</v>
       </c>
       <c r="O94" s="12">
         <f>IF((K94-J94)&lt;0,0,(K94-J94))</f>
@@ -11480,14 +11527,14 @@
       </c>
       <c r="P94" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3648</v>
+        <v>4392</v>
       </c>
       <c r="Q94" s="12"/>
       <c r="R94" s="10"/>
       <c r="S94" s="12"/>
       <c r="T94" s="12">
         <f>IF((P94-Q94)&lt;0,0,(P94-Q94))</f>
-        <v>3648</v>
+        <v>4392</v>
       </c>
       <c r="U94" s="12">
         <f>IF((Q94-P94)&lt;0,0,(Q94-P94))</f>
@@ -11495,14 +11542,14 @@
       </c>
       <c r="V94" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3648</v>
+        <v>4392</v>
       </c>
       <c r="W94" s="12"/>
       <c r="X94" s="10"/>
       <c r="Y94" s="12"/>
       <c r="Z94" s="12">
         <f>IF((V94-W94)&lt;0,0,(V94-W94))</f>
-        <v>3648</v>
+        <v>4392</v>
       </c>
       <c r="AA94" s="12">
         <f>IF((W94-V94)&lt;0,0,(W94-V94))</f>
@@ -11513,10 +11560,10 @@
       <c r="A95" s="10">
         <v>10</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C95" s="10">
+      <c r="C95" s="43">
         <v>456</v>
       </c>
       <c r="D95" s="12">
@@ -11584,10 +11631,10 @@
       <c r="A96" s="10">
         <v>10</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C96" s="10">
+      <c r="C96" s="43">
         <v>456</v>
       </c>
       <c r="D96" s="12">
@@ -11655,10 +11702,10 @@
       <c r="A97" s="10">
         <v>10</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C97" s="10">
+      <c r="C97" s="43">
         <v>456</v>
       </c>
       <c r="D97" s="12">
@@ -11726,10 +11773,10 @@
       <c r="A98" s="10">
         <v>10</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B98" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C98" s="10">
+      <c r="C98" s="43">
         <v>456</v>
       </c>
       <c r="D98" s="12">
@@ -11797,10 +11844,10 @@
       <c r="A99" s="10">
         <v>10</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="C99" s="10">
+      <c r="C99" s="43">
         <v>456</v>
       </c>
       <c r="D99" s="12">
@@ -11868,10 +11915,10 @@
       <c r="A100" s="10">
         <v>10</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C100" s="10">
+      <c r="C100" s="43">
         <v>456</v>
       </c>
       <c r="D100" s="12">
@@ -11939,10 +11986,10 @@
       <c r="A101" s="10">
         <v>10</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C101" s="10">
+      <c r="C101" s="43">
         <v>456</v>
       </c>
       <c r="D101" s="12">
@@ -13661,38 +13708,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -22185,18 +22232,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F55:F65 F43:F53 F31:F41 F3:F10 F12:F19 F21:F29 F67:F77 F103:F113 F79:F89 F91:F101 F115:F122" xr:uid="{63226F9B-EADA-48D4-84A5-E00FED121F0D}">
       <formula1>"2024,2025,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{38420060-D4A3-4BED-855F-882467D575DC}">
-      <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
